--- a/Dic_Kategorien.xlsx
+++ b/Dic_Kategorien.xlsx
@@ -435,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="21.53125"/>
@@ -1371,17 +1371,17 @@
     <row outlineLevel="0" r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>K_RISKEXT</t>
+          <t>K_RECEIVER</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Gefährdungskategorie</t>
+          <t>Art der Empfänger/Bereitsteller</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Level of risk of extinction</t>
+          <t>Type of receiver/provider</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row outlineLevel="0" r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>K_SCHUTZBEREICH</t>
+          <t>K_RISKEXT</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Umweltschutz- und/oder Ressourcenmanagementbereich</t>
+          <t>Gefährdungskategorie</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Environmental protection and/or resource management sector</t>
+          <t>Level of risk of extinction</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>K_SCORE</t>
+          <t>K_ROLE</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Punktzahl</t>
+          <t>Rolle</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>K_SDG</t>
+          <t>K_SCHUTZBEREICH</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Ziel</t>
+          <t>Umweltschutz- und/oder Ressourcenmanagementbereich</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Environmental protection and/or resource management sector</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>K_SEA</t>
+          <t>K_SCORE</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Meer</t>
+          <t>Punktzahl</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>K_SECTION</t>
+          <t>K_SDG</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Aufgabenbereich</t>
+          <t>Ziel</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Field of work</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row outlineLevel="0" r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>K_SECTIONS</t>
+          <t>K_SEA</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Abschnitt</t>
+          <t>Meer</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row outlineLevel="0" r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>K_SEKTOR</t>
+          <t>K_SECTION</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Sektor</t>
+          <t>Aufgabenbereich</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Field of work</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row outlineLevel="0" r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>K_SERIES</t>
+          <t>K_SECTIONS</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Zeitreihe</t>
+          <t>Abschnitt</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Time series</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1569,39 +1569,39 @@
     <row outlineLevel="0" r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>K_SEX</t>
+          <t>K_SEKTOR</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Geschlecht</t>
+          <t>Sektor</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Geschlecht</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>K_SKILL</t>
+          <t>K_SENDER</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Fähigkeit</t>
+          <t>Art der Bereitsteller</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Type of provider</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row outlineLevel="0" r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>K_SOURCE</t>
+          <t>K_SERIES</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Datenquelle</t>
+          <t>Zeitreihe</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Data source</t>
+          <t>Time series</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1635,39 +1635,39 @@
     <row outlineLevel="0" r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>K_SPEED</t>
+          <t>K_SEX</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Geschwindigkeit</t>
+          <t>Geschlecht</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Geschwindigkeit</t>
+          <t>Geschlecht</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>K_STDACCNTSYS</t>
+          <t>K_SKILL</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Standardrechnungssystem (der Volkswirtschaftlichen Gesamtrechnungen)</t>
+          <t>Fähigkeit</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Standard accounting system</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row outlineLevel="0" r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>K_SUBJCT</t>
+          <t>K_SOURCE</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Schulfach</t>
+          <t>Datenquelle</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Data source</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1701,61 +1701,61 @@
     <row outlineLevel="0" r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>K_SUBSTANCE</t>
+          <t>K_SPEED</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Substanz</t>
+          <t>Geschwindigkeit</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Substance</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>Geschwindigkeit</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>K_TECHNO</t>
+          <t>K_STDACCNTSYS</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Technologie</t>
+          <t>Standardrechnungssystem (der Volkswirtschaftlichen Gesamtrechnungen)</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Standard accounting system</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Technologie</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>K_TECHNOINT</t>
+          <t>K_SUBJCT</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Technologiesektoren</t>
+          <t>Schulfach</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Technology sectors</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>K_THEMATICAREA</t>
+          <t>K_SUBSTANCE</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Themenbereich</t>
+          <t>Substanz</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Thematic area</t>
+          <t>Substance</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1789,39 +1789,39 @@
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>K_TOURISINDUS</t>
+          <t>K_TECHNO</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Wirtschaftszweig</t>
+          <t>Technologie</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Tourism Industries</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>Technologie</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>K_TRANSPTY</t>
+          <t>K_TECHNOINT</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Verkehrsträger</t>
+          <t>Technologiesektoren</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Mode of transport</t>
+          <t>Technology sectors</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row outlineLevel="0" r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>K_TYPDISEASE</t>
+          <t>K_THEMATICAREA</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Erkrankung</t>
+          <t>Themenbereich</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Disease</t>
+          <t>Thematic area</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1855,39 +1855,39 @@
     <row outlineLevel="0" r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>K_TYPEABUSE</t>
+          <t>K_TOURISINDUS</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Form der Misshandlung</t>
+          <t>Wirtschaftszweig</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Form of abuse</t>
+          <t>Tourism Industries</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Art der Gewalt</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>K_TYPEACCOUNT</t>
+          <t>K_TRANSPTY</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Kontenart</t>
+          <t>Verkehrsträger</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Type of account</t>
+          <t>Mode of transport</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>K_TYPEBIOMASS</t>
+          <t>K_TYPDISEASE</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Art der Biomasse</t>
+          <t>Erkrankung</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Type of biomass</t>
+          <t>Disease</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1921,83 +1921,83 @@
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>K_TYPECLASS</t>
+          <t>K_TYPEABUSE</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Art der Klassifikation</t>
+          <t>Form der Misshandlung</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Type of classification</t>
+          <t>Form of abuse</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>Art der Gewalt</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>K_TYPEEXPLOITATION</t>
+          <t>K_TYPEACCOUNT</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Form der Ausbeutung</t>
+          <t>Kontenart</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Form of exploitation</t>
+          <t>Type of account</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Form der Ausbeutung</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>K_TYPEFLOW</t>
+          <t>K_TYPEBIOMASS</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Art des Finanzstroms</t>
+          <t>Art der Biomasse</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Type of flow</t>
+          <t>Type of biomass</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Art des Zahlungsstroms</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>K_TYPEWASTE</t>
+          <t>K_TYPECLASS</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Abfallart</t>
+          <t>Art der Klassifikation</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Type of waste</t>
+          <t>Type of classification</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2009,61 +2009,61 @@
     <row outlineLevel="0" r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>K_TYPHARRAS</t>
+          <t>K_TYPEEXPLOITATION</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Art der Belästigung</t>
+          <t>Form der Ausbeutung</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Type of harassment</t>
+          <t>Form of exploitation</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>Form der Ausbeutung</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>K_TYPPHYSVIOL</t>
+          <t>K_TYPEFLOW</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Art der physischen Gewalt</t>
+          <t>Art des Finanzstroms</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Type of physical violence</t>
+          <t>Type of flow</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>Art des Zahlungsstroms</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>K_TYPPSYCHVIOL</t>
+          <t>K_TYPEWASTE</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Art der psychischen Gewalt</t>
+          <t>Abfallart</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Type of psycological violence</t>
+          <t>Type of waste</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row outlineLevel="0" r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>K_TYPSEXVIOL</t>
+          <t>K_TYPHARRAS</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Art der sexuellen Gewalt</t>
+          <t>Art der Belästigung</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Type of sexual violence</t>
+          <t>Type of harassment</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>K_TYPVIOL</t>
+          <t>K_TYPPHYSVIOL</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Art der Gewalt</t>
+          <t>Art der physischen Gewalt</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Type of violence</t>
+          <t>Type of physical violence</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>K_UNPAIDWORK</t>
+          <t>K_TYPPSYCHVIOL</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Art der unbezahlten Arbeit</t>
+          <t>Art der psychischen Gewalt</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Type of unpaid work</t>
+          <t>Type of psychological violence</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>K_URBAN</t>
+          <t>K_TYPSEXVIOL</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Verstädterungsgrad</t>
+          <t>Art der sexuellen Gewalt</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Degree of urbanisation</t>
+          <t>Type of sexual violence</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2163,39 +2163,39 @@
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>K_WASTETREATMNT</t>
+          <t>K_TYPVIOL</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Art der Abfallbehandlung</t>
+          <t>Art der Gewalt</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Type of waste treatment</t>
+          <t>Type of violence</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Art der Behandlung</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>K_WASTEWATER</t>
+          <t>K_UNPAIDWORK</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Art des Abwassers</t>
+          <t>Art der unbezahlten Arbeit</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Type of waste water</t>
+          <t>Type of unpaid work</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2207,20 +2207,86 @@
     <row outlineLevel="0" r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
+          <t>K_URBAN</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Verstädterungsgrad</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Degree of urbanisation</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>K_WASTETREATMNT</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Art der Abfallbehandlung</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Type of waste treatment</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Art der Behandlung</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>K_WASTEWATER</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Art des Abwassers</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Type of waste water</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
           <t>K_WATERTREATMNT</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>Behandlung</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Treatment</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t/>
         </is>
